--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/48.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/48.xlsx
@@ -426,13 +426,13 @@
         <v>-19.68485417376838</v>
       </c>
       <c r="E2">
-        <v>-30.45805181947564</v>
+        <v>-30.43722310327736</v>
       </c>
       <c r="F2">
-        <v>-3.019111886962934</v>
+        <v>-2.554872428514216</v>
       </c>
       <c r="G2">
-        <v>-19.93996813953098</v>
+        <v>-21.76282072436448</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.28193497497788</v>
       </c>
       <c r="E3">
-        <v>-28.75833891391065</v>
+        <v>-31.11771009969897</v>
       </c>
       <c r="F3">
-        <v>-2.777157365748838</v>
+        <v>-2.496687073774176</v>
       </c>
       <c r="G3">
-        <v>-20.20671038053945</v>
+        <v>-21.51595334350103</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.80890949919106</v>
       </c>
       <c r="E4">
-        <v>-29.90452512033307</v>
+        <v>-30.85956443889172</v>
       </c>
       <c r="F4">
-        <v>-3.446912291729905</v>
+        <v>-2.329647615367058</v>
       </c>
       <c r="G4">
-        <v>-21.13218166240656</v>
+        <v>-21.00868672688236</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.30361093772043</v>
       </c>
       <c r="E5">
-        <v>-32.35650586381525</v>
+        <v>-32.60380130090012</v>
       </c>
       <c r="F5">
-        <v>-2.624751845879576</v>
+        <v>-2.33539151493807</v>
       </c>
       <c r="G5">
-        <v>-20.15736669927661</v>
+        <v>-20.85643970334958</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.75525795106126</v>
       </c>
       <c r="E6">
-        <v>-31.14177893904974</v>
+        <v>-31.69132963801357</v>
       </c>
       <c r="F6">
-        <v>-2.535095156772377</v>
+        <v>-2.218220602546885</v>
       </c>
       <c r="G6">
-        <v>-20.22474126681909</v>
+        <v>-20.84963322172084</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.19517332817675</v>
       </c>
       <c r="E7">
-        <v>-32.31179623993752</v>
+        <v>-32.07975270331048</v>
       </c>
       <c r="F7">
-        <v>-2.424585975034507</v>
+        <v>-2.069464869454359</v>
       </c>
       <c r="G7">
-        <v>-19.94632273169361</v>
+        <v>-20.18569172691062</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.65332743945283</v>
       </c>
       <c r="E8">
-        <v>-32.78485195596379</v>
+        <v>-33.24606118398599</v>
       </c>
       <c r="F8">
-        <v>-2.103606860328143</v>
+        <v>-2.100514564813492</v>
       </c>
       <c r="G8">
-        <v>-19.33313024472765</v>
+        <v>-19.5898862251169</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.15424973757112</v>
       </c>
       <c r="E9">
-        <v>-32.19725981109852</v>
+        <v>-32.823948536309</v>
       </c>
       <c r="F9">
-        <v>-2.101379380382015</v>
+        <v>-2.091176379081733</v>
       </c>
       <c r="G9">
-        <v>-18.80147649439393</v>
+        <v>-19.67208044976593</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.71906233664509</v>
       </c>
       <c r="E10">
-        <v>-32.71045139225476</v>
+        <v>-33.54323776226534</v>
       </c>
       <c r="F10">
-        <v>-2.066145601271341</v>
+        <v>-2.093123870845715</v>
       </c>
       <c r="G10">
-        <v>-20.0621537542944</v>
+        <v>-19.06396302911167</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.39920854089199</v>
       </c>
       <c r="E11">
-        <v>-33.58276228340429</v>
+        <v>-34.5642841179598</v>
       </c>
       <c r="F11">
-        <v>-2.237414703637153</v>
+        <v>-1.835475929185582</v>
       </c>
       <c r="G11">
-        <v>-20.13787089659584</v>
+        <v>-18.29316209011207</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.2224474858948</v>
       </c>
       <c r="E12">
-        <v>-34.28321758596272</v>
+        <v>-34.91995499499624</v>
       </c>
       <c r="F12">
-        <v>-2.247699713310312</v>
+        <v>-1.857327432904031</v>
       </c>
       <c r="G12">
-        <v>-17.95020778024405</v>
+        <v>-18.46213233443648</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.18660658491644</v>
       </c>
       <c r="E13">
-        <v>-34.31538560107622</v>
+        <v>-35.11972862584462</v>
       </c>
       <c r="F13">
-        <v>-1.671993480406086</v>
+        <v>-1.597939091330616</v>
       </c>
       <c r="G13">
-        <v>-18.648267757382</v>
+        <v>-18.05163130865793</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.32077096215888</v>
       </c>
       <c r="E14">
-        <v>-36.0159883517837</v>
+        <v>-35.17973317068325</v>
       </c>
       <c r="F14">
-        <v>-1.447988024075849</v>
+        <v>-1.644087439340576</v>
       </c>
       <c r="G14">
-        <v>-17.56624077696275</v>
+        <v>-17.78549489748315</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.62420192358467</v>
       </c>
       <c r="E15">
-        <v>-36.09505550795762</v>
+        <v>-36.18215844125816</v>
       </c>
       <c r="F15">
-        <v>-2.018381108458519</v>
+        <v>-1.324687192903948</v>
       </c>
       <c r="G15">
-        <v>-16.98056885506475</v>
+        <v>-17.25844115017625</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.06638736133908</v>
       </c>
       <c r="E16">
-        <v>-35.46630859131065</v>
+        <v>-36.70016379028456</v>
       </c>
       <c r="F16">
-        <v>-0.9788984744837396</v>
+        <v>-1.302735456729762</v>
       </c>
       <c r="G16">
-        <v>-16.52540360414313</v>
+        <v>-17.36296169394212</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.61824816811099</v>
       </c>
       <c r="E17">
-        <v>-36.20041045574608</v>
+        <v>-36.83184502171661</v>
       </c>
       <c r="F17">
-        <v>-2.011323418186667</v>
+        <v>-0.811574057690059</v>
       </c>
       <c r="G17">
-        <v>-16.2639251305421</v>
+        <v>-16.87325255559097</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-17.24846862310849</v>
       </c>
       <c r="E18">
-        <v>-38.80734425858572</v>
+        <v>-37.55019685355335</v>
       </c>
       <c r="F18">
-        <v>-1.194830662106292</v>
+        <v>-0.7912293542773031</v>
       </c>
       <c r="G18">
-        <v>-16.13996009755132</v>
+        <v>-16.57468107449518</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-17.9004004900573</v>
       </c>
       <c r="E19">
-        <v>-38.85555212863437</v>
+        <v>-38.23952343123794</v>
       </c>
       <c r="F19">
-        <v>-1.466259323879398</v>
+        <v>-0.7942951420350641</v>
       </c>
       <c r="G19">
-        <v>-15.62161970610378</v>
+        <v>-16.61086864778495</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-18.5030674000004</v>
       </c>
       <c r="E20">
-        <v>-37.00738905238694</v>
+        <v>-38.93725712091776</v>
       </c>
       <c r="F20">
-        <v>-0.6818757450663376</v>
+        <v>-0.4494582177606719</v>
       </c>
       <c r="G20">
-        <v>-15.20675207075893</v>
+        <v>-16.50825663352247</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-19.02159576098984</v>
       </c>
       <c r="E21">
-        <v>-39.49834637165314</v>
+        <v>-38.80424225389046</v>
       </c>
       <c r="F21">
-        <v>-0.8927076745898538</v>
+        <v>-0.4009117461196069</v>
       </c>
       <c r="G21">
-        <v>-16.46078009994378</v>
+        <v>-16.39532564881408</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-19.41123489739816</v>
       </c>
       <c r="E22">
-        <v>-41.18801512186911</v>
+        <v>-40.07071378690462</v>
       </c>
       <c r="F22">
-        <v>-1.61801126186785</v>
+        <v>-0.5397933397707636</v>
       </c>
       <c r="G22">
-        <v>-15.07203935167491</v>
+        <v>-16.60406216615621</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-19.62460380280469</v>
       </c>
       <c r="E23">
-        <v>-40.3771714726627</v>
+        <v>-40.33775789913695</v>
       </c>
       <c r="F23">
-        <v>-1.477639435259057</v>
+        <v>-0.5038156867323754</v>
       </c>
       <c r="G23">
-        <v>-15.92157333996222</v>
+        <v>-16.2252364400974</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-19.65819578083826</v>
       </c>
       <c r="E24">
-        <v>-40.86573494792823</v>
+        <v>-39.85585580913669</v>
       </c>
       <c r="F24">
-        <v>-0.9667604069305183</v>
+        <v>-0.2449980902994895</v>
       </c>
       <c r="G24">
-        <v>-16.13706337020446</v>
+        <v>-16.14939018651993</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-19.5167996555406</v>
       </c>
       <c r="E25">
-        <v>-40.36596576373072</v>
+        <v>-40.01096736508443</v>
       </c>
       <c r="F25">
-        <v>-0.4624122272056506</v>
+        <v>-0.299124444765812</v>
       </c>
       <c r="G25">
-        <v>-15.95299538294821</v>
+        <v>-15.79712662259547</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-19.20636059345134</v>
       </c>
       <c r="E26">
-        <v>-40.03044433179141</v>
+        <v>-40.62933049083181</v>
       </c>
       <c r="F26">
-        <v>-1.082062522460987</v>
+        <v>-0.454424280340455</v>
       </c>
       <c r="G26">
-        <v>-14.25455475475329</v>
+        <v>-16.12990597074855</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-18.75173739942463</v>
       </c>
       <c r="E27">
-        <v>-39.60484023065452</v>
+        <v>-40.7639325879988</v>
       </c>
       <c r="F27">
-        <v>-2.106229471525406</v>
+        <v>-0.436604440771432</v>
       </c>
       <c r="G27">
-        <v>-14.24505348905558</v>
+        <v>-15.84245130157364</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-18.20090068782194</v>
       </c>
       <c r="E28">
-        <v>-39.9144248277149</v>
+        <v>-40.53047390324437</v>
       </c>
       <c r="F28">
-        <v>-1.649553007464247</v>
+        <v>-0.3680495828831477</v>
       </c>
       <c r="G28">
-        <v>-13.96590166809316</v>
+        <v>-15.80720226794425</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-17.59331324114632</v>
       </c>
       <c r="E29">
-        <v>-39.76890684395242</v>
+        <v>-40.33773978524091</v>
       </c>
       <c r="F29">
-        <v>-0.7299616444314461</v>
+        <v>-0.5982040104443651</v>
       </c>
       <c r="G29">
-        <v>-15.35111006427162</v>
+        <v>-16.1742391413377</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-16.95625007083014</v>
       </c>
       <c r="E30">
-        <v>-39.0556472811373</v>
+        <v>-39.62669464621554</v>
       </c>
       <c r="F30">
-        <v>-1.275410101213614</v>
+        <v>-0.6117006005381774</v>
       </c>
       <c r="G30">
-        <v>-14.49822414862581</v>
+        <v>-15.73708822396802</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-16.34934536142996</v>
       </c>
       <c r="E31">
-        <v>-38.42306248276882</v>
+        <v>-40.22864884639613</v>
       </c>
       <c r="F31">
-        <v>-0.8576354271227254</v>
+        <v>-0.4798882943025117</v>
       </c>
       <c r="G31">
-        <v>-13.67571579884834</v>
+        <v>-15.81930893298136</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-15.80656495541721</v>
       </c>
       <c r="E32">
-        <v>-39.91058241751939</v>
+        <v>-39.61269260458382</v>
       </c>
       <c r="F32">
-        <v>-0.471425692915512</v>
+        <v>-0.4221121530594547</v>
       </c>
       <c r="G32">
-        <v>-15.65152717450556</v>
+        <v>-16.11061873243676</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-15.33633017797498</v>
       </c>
       <c r="E33">
-        <v>-41.03157219456313</v>
+        <v>-39.61143368880969</v>
       </c>
       <c r="F33">
-        <v>-1.553776339985166</v>
+        <v>-0.3117653313325325</v>
       </c>
       <c r="G33">
-        <v>-15.20204447500209</v>
+        <v>-16.33028832642233</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-14.96273063917358</v>
       </c>
       <c r="E34">
-        <v>-38.66831331383923</v>
+        <v>-39.05060482532976</v>
       </c>
       <c r="F34">
-        <v>-0.9974729567567129</v>
+        <v>-0.3881250668899937</v>
       </c>
       <c r="G34">
-        <v>-15.17940199878625</v>
+        <v>-15.87900634541827</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-14.69458925894246</v>
       </c>
       <c r="E35">
-        <v>-37.3777706772373</v>
+        <v>-39.04127164039995</v>
       </c>
       <c r="F35">
-        <v>-0.344349163121651</v>
+        <v>-0.6399512424432519</v>
       </c>
       <c r="G35">
-        <v>-14.8587226945792</v>
+        <v>-16.28625972602279</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-14.51691781987913</v>
       </c>
       <c r="E36">
-        <v>-36.65263066286305</v>
+        <v>-38.50973294680163</v>
       </c>
       <c r="F36">
-        <v>-1.158747806407749</v>
+        <v>-0.7440182108895509</v>
       </c>
       <c r="G36">
-        <v>-15.72373844908091</v>
+        <v>-16.26652390879043</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-14.41103625670251</v>
       </c>
       <c r="E37">
-        <v>-38.18652217145217</v>
+        <v>-38.13490662471274</v>
       </c>
       <c r="F37">
-        <v>-1.269161725894298</v>
+        <v>-0.8357565872799849</v>
       </c>
       <c r="G37">
-        <v>-15.54889860751538</v>
+        <v>-16.196540631363</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-14.37286423287728</v>
       </c>
       <c r="E38">
-        <v>-38.15220313118504</v>
+        <v>-37.85667038897046</v>
       </c>
       <c r="F38">
-        <v>-0.7599941046199422</v>
+        <v>-0.5843106323646118</v>
       </c>
       <c r="G38">
-        <v>-16.0282192539643</v>
+        <v>-16.85304498561926</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-14.37988581022275</v>
       </c>
       <c r="E39">
-        <v>-35.60984536769477</v>
+        <v>-37.79608846369585</v>
       </c>
       <c r="F39">
-        <v>-1.262096580315821</v>
+        <v>-0.4612707369245929</v>
       </c>
       <c r="G39">
-        <v>-14.67179108543148</v>
+        <v>-16.43309566287163</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-14.39434488939657</v>
       </c>
       <c r="E40">
-        <v>-37.72580201862279</v>
+        <v>-37.50680954408587</v>
       </c>
       <c r="F40">
-        <v>-1.68222381783066</v>
+        <v>-0.333061828891105</v>
       </c>
       <c r="G40">
-        <v>-16.60452233198617</v>
+        <v>-16.10579526758604</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-14.41409166468393</v>
       </c>
       <c r="E41">
-        <v>-36.2782345458049</v>
+        <v>-37.42444792307136</v>
       </c>
       <c r="F41">
-        <v>-0.9985837974438669</v>
+        <v>-0.2625155757664907</v>
       </c>
       <c r="G41">
-        <v>-16.00304586568368</v>
+        <v>-16.46282601708705</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-14.42285886579165</v>
       </c>
       <c r="E42">
-        <v>-37.22530375011005</v>
+        <v>-37.10537617296492</v>
       </c>
       <c r="F42">
-        <v>-1.058197257586333</v>
+        <v>-0.3896931663834932</v>
       </c>
       <c r="G42">
-        <v>-15.75914969944172</v>
+        <v>-16.18184180916864</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-14.39603994973195</v>
       </c>
       <c r="E43">
-        <v>-35.78131150752121</v>
+        <v>-36.69832522983745</v>
       </c>
       <c r="F43">
-        <v>-1.025462662929905</v>
+        <v>-0.3781556651973016</v>
       </c>
       <c r="G43">
-        <v>-15.841090667357</v>
+        <v>-15.9791023450709</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-14.33079541014028</v>
       </c>
       <c r="E44">
-        <v>-34.88709865183358</v>
+        <v>-36.23147125896469</v>
       </c>
       <c r="F44">
-        <v>-0.5766722565433976</v>
+        <v>-0.5914677267247995</v>
       </c>
       <c r="G44">
-        <v>-15.94307864378532</v>
+        <v>-16.94732104621385</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-14.23155705363544</v>
       </c>
       <c r="E45">
-        <v>-34.54399202593143</v>
+        <v>-35.16523299691069</v>
       </c>
       <c r="F45">
-        <v>-0.4539869023517768</v>
+        <v>-0.4187705189565614</v>
       </c>
       <c r="G45">
-        <v>-15.68316605822437</v>
+        <v>-16.69924531622856</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-14.09536730278697</v>
       </c>
       <c r="E46">
-        <v>-34.58200630098882</v>
+        <v>-34.56134966680283</v>
       </c>
       <c r="F46">
-        <v>-0.2766582924344866</v>
+        <v>-0.5752623752238328</v>
       </c>
       <c r="G46">
-        <v>-18.25039811810854</v>
+        <v>-16.70003157079414</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.91949549784607</v>
       </c>
       <c r="E47">
-        <v>-32.37846443427844</v>
+        <v>-33.77512733077612</v>
       </c>
       <c r="F47">
-        <v>-0.4467535981905315</v>
+        <v>-0.308218262113745</v>
       </c>
       <c r="G47">
-        <v>-16.21302052705749</v>
+        <v>-16.49552427537843</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.72558448344073</v>
       </c>
       <c r="E48">
-        <v>-33.3319708643855</v>
+        <v>-34.71350639346055</v>
       </c>
       <c r="F48">
-        <v>-0.3795539493732272</v>
+        <v>-0.4924662249466195</v>
       </c>
       <c r="G48">
-        <v>-14.55151068962592</v>
+        <v>-16.82589851219723</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.52283579783754</v>
       </c>
       <c r="E49">
-        <v>-32.68011967335139</v>
+        <v>-34.07962871576289</v>
       </c>
       <c r="F49">
-        <v>-0.3869769496697136</v>
+        <v>-0.4842753280677379</v>
       </c>
       <c r="G49">
-        <v>-17.21064018313471</v>
+        <v>-16.32387579971276</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.30620370756064</v>
       </c>
       <c r="E50">
-        <v>-31.60526372526079</v>
+        <v>-33.90759425244849</v>
       </c>
       <c r="F50">
-        <v>-0.6806232535533048</v>
+        <v>-0.4398127077224744</v>
       </c>
       <c r="G50">
-        <v>-16.70089231263435</v>
+        <v>-16.47550209595692</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.09766875388178</v>
       </c>
       <c r="E51">
-        <v>-32.40891162926901</v>
+        <v>-32.76912682997215</v>
       </c>
       <c r="F51">
-        <v>-0.2277373987273562</v>
+        <v>-0.1902156688501498</v>
       </c>
       <c r="G51">
-        <v>-17.19112782772624</v>
+        <v>-17.53837425988594</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.9065539947805</v>
       </c>
       <c r="E52">
-        <v>-31.47110089007255</v>
+        <v>-32.66730409190968</v>
       </c>
       <c r="F52">
-        <v>-0.3171538612877433</v>
+        <v>-0.3674059414111725</v>
       </c>
       <c r="G52">
-        <v>-17.57527360046666</v>
+        <v>-17.07416956436933</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.72886561004977</v>
       </c>
       <c r="E53">
-        <v>-31.71245270502235</v>
+        <v>-32.76403456095053</v>
       </c>
       <c r="F53">
-        <v>-0.2206167525328917</v>
+        <v>-0.411455206422439</v>
       </c>
       <c r="G53">
-        <v>-17.23121522366128</v>
+        <v>-16.85813991520419</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.56894714982486</v>
       </c>
       <c r="E54">
-        <v>-32.34573488838801</v>
+        <v>-32.2915947173893</v>
       </c>
       <c r="F54">
-        <v>-0.5855067948942543</v>
+        <v>-0.4213409430074483</v>
       </c>
       <c r="G54">
-        <v>-17.2675583925914</v>
+        <v>-16.75511573802207</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.43677854092937</v>
       </c>
       <c r="E55">
-        <v>-30.96807346882651</v>
+        <v>-32.66872150427408</v>
       </c>
       <c r="F55">
-        <v>0.2483593107250344</v>
+        <v>-0.209741116901537</v>
       </c>
       <c r="G55">
-        <v>-16.42468687720188</v>
+        <v>-16.59737486416688</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.32893905015684</v>
       </c>
       <c r="E56">
-        <v>-29.56882934214446</v>
+        <v>-31.70850613992466</v>
       </c>
       <c r="F56">
-        <v>-0.5242945856643848</v>
+        <v>-0.3230775165851625</v>
       </c>
       <c r="G56">
-        <v>-18.55485905971869</v>
+        <v>-17.00373770802134</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.23212623377775</v>
       </c>
       <c r="E57">
-        <v>-29.13868091734088</v>
+        <v>-31.23571307539084</v>
       </c>
       <c r="F57">
-        <v>-0.398700833521535</v>
+        <v>-0.5594645804850434</v>
       </c>
       <c r="G57">
-        <v>-17.59544640971021</v>
+        <v>-17.20282067457095</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.15758423417771</v>
       </c>
       <c r="E58">
-        <v>-29.15825298200203</v>
+        <v>-31.44273905736251</v>
       </c>
       <c r="F58">
-        <v>-0.8825684575795878</v>
+        <v>-0.5542268133971422</v>
       </c>
       <c r="G58">
-        <v>-17.24088367190872</v>
+        <v>-16.95276027253487</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.10089769721257</v>
       </c>
       <c r="E59">
-        <v>-27.82760617958817</v>
+        <v>-31.08823879085705</v>
       </c>
       <c r="F59">
-        <v>-0.09459887627980849</v>
+        <v>-0.4956985145523431</v>
       </c>
       <c r="G59">
-        <v>-17.70354399793126</v>
+        <v>-17.45498492829724</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.04521903251367</v>
       </c>
       <c r="E60">
-        <v>-28.99874201355585</v>
+        <v>-30.33898918086597</v>
       </c>
       <c r="F60">
-        <v>-0.01492567111114924</v>
+        <v>-0.6248998067343848</v>
       </c>
       <c r="G60">
-        <v>-16.55708883549949</v>
+        <v>-17.10190862544289</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.99611644517385</v>
       </c>
       <c r="E61">
-        <v>-28.11513710823119</v>
+        <v>-31.10176987119197</v>
       </c>
       <c r="F61">
-        <v>-0.2916227495660597</v>
+        <v>-0.3684687367889642</v>
       </c>
       <c r="G61">
-        <v>-17.27003964647308</v>
+        <v>-16.83643597864873</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.95407323460311</v>
       </c>
       <c r="E62">
-        <v>-28.77711849562046</v>
+        <v>-30.88802816226693</v>
       </c>
       <c r="F62">
-        <v>-0.5262230249781021</v>
+        <v>-0.4751533462281098</v>
       </c>
       <c r="G62">
-        <v>-16.68827085776588</v>
+        <v>-17.5280900501682</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.91003991940382</v>
       </c>
       <c r="E63">
-        <v>-27.63239725053953</v>
+        <v>-30.4103851020709</v>
       </c>
       <c r="F63">
-        <v>-0.7101893428940247</v>
+        <v>-0.7244364338547734</v>
       </c>
       <c r="G63">
-        <v>-16.96902167222377</v>
+        <v>-16.81925093675438</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.86005412931049</v>
       </c>
       <c r="E64">
-        <v>-28.51019212371234</v>
+        <v>-30.88578883187014</v>
       </c>
       <c r="F64">
-        <v>0.0310710856640989</v>
+        <v>-0.7329586776947747</v>
       </c>
       <c r="G64">
-        <v>-18.00680652205619</v>
+        <v>-17.40176459820792</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.81283562579662</v>
       </c>
       <c r="E65">
-        <v>-26.42404188870281</v>
+        <v>-30.57599366076841</v>
       </c>
       <c r="F65">
-        <v>-0.6483666268882919</v>
+        <v>-0.5834292494480332</v>
       </c>
       <c r="G65">
-        <v>-17.8036615161299</v>
+        <v>-17.35546496356844</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.76673173417282</v>
       </c>
       <c r="E66">
-        <v>-29.67908183457221</v>
+        <v>-30.50884544818267</v>
       </c>
       <c r="F66">
-        <v>-0.7449335568696444</v>
+        <v>-0.6975733073493883</v>
       </c>
       <c r="G66">
-        <v>-18.29955806409395</v>
+        <v>-16.96086448801501</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.70942259953871</v>
       </c>
       <c r="E67">
-        <v>-29.12997719029813</v>
+        <v>-30.83958934004389</v>
       </c>
       <c r="F67">
-        <v>-0.6553282265414191</v>
+        <v>-0.5163588259455656</v>
       </c>
       <c r="G67">
-        <v>-17.86689955702106</v>
+        <v>-17.34690885862219</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.65444424243294</v>
       </c>
       <c r="E68">
-        <v>-27.54091754711058</v>
+        <v>-30.31217155779254</v>
       </c>
       <c r="F68">
-        <v>-0.5213422842408074</v>
+        <v>-0.9490880167591937</v>
       </c>
       <c r="G68">
-        <v>-16.43676209205637</v>
+        <v>-18.10209726485858</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.60235073060782</v>
       </c>
       <c r="E69">
-        <v>-28.62705845242829</v>
+        <v>-30.28210701885562</v>
       </c>
       <c r="F69">
-        <v>-1.008002334813697</v>
+        <v>-0.768787224600659</v>
       </c>
       <c r="G69">
-        <v>-17.11466581267847</v>
+        <v>-17.37421754877564</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.54287139570965</v>
       </c>
       <c r="E70">
-        <v>-27.9279299927541</v>
+        <v>-29.80892450555714</v>
       </c>
       <c r="F70">
-        <v>-0.7370019389878391</v>
+        <v>-0.569568177696989</v>
       </c>
       <c r="G70">
-        <v>-17.08458785118142</v>
+        <v>-16.9019086377789</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.4809059702262</v>
       </c>
       <c r="E71">
-        <v>-28.15069468613942</v>
+        <v>-30.00844680609809</v>
       </c>
       <c r="F71">
-        <v>-1.019539835999889</v>
+        <v>-0.7438434253675602</v>
       </c>
       <c r="G71">
-        <v>-16.56703371429946</v>
+        <v>-16.88779578214498</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.41967246305979</v>
       </c>
       <c r="E72">
-        <v>-29.91130198168555</v>
+        <v>-29.70891315709774</v>
       </c>
       <c r="F72">
-        <v>-1.118775765753061</v>
+        <v>-0.7391209028042003</v>
       </c>
       <c r="G72">
-        <v>-17.55137477221866</v>
+        <v>-17.13599731286076</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.35209505226132</v>
       </c>
       <c r="E73">
-        <v>-27.97169316556423</v>
+        <v>-30.25652114071228</v>
       </c>
       <c r="F73">
-        <v>-0.9603952318074069</v>
+        <v>-0.96466298066663</v>
       </c>
       <c r="G73">
-        <v>-15.77939699595991</v>
+        <v>-17.67805445255164</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.27076001430168</v>
       </c>
       <c r="E74">
-        <v>-28.57178389869066</v>
+        <v>-30.10391156665379</v>
       </c>
       <c r="F74">
-        <v>-0.2589494540974388</v>
+        <v>-0.8755952607828216</v>
       </c>
       <c r="G74">
-        <v>-16.15701437289687</v>
+        <v>-17.212772174462</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.18357637911947</v>
       </c>
       <c r="E75">
-        <v>-27.41065146380593</v>
+        <v>-30.19196095102193</v>
       </c>
       <c r="F75">
-        <v>-1.309841192310976</v>
+        <v>-0.9323690774684913</v>
       </c>
       <c r="G75">
-        <v>-17.2885025589456</v>
+        <v>-16.89652734600481</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.08796452294429</v>
       </c>
       <c r="E76">
-        <v>-29.3625686722801</v>
+        <v>-30.83787984110599</v>
       </c>
       <c r="F76">
-        <v>-1.461632891934763</v>
+        <v>-1.286072846422449</v>
       </c>
       <c r="G76">
-        <v>-15.5201415536885</v>
+        <v>-16.79089114839221</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.97073106003109</v>
       </c>
       <c r="E77">
-        <v>-28.36222876398572</v>
+        <v>-31.11734102906734</v>
       </c>
       <c r="F77">
-        <v>-0.7466052022884938</v>
+        <v>-0.9835514141852644</v>
       </c>
       <c r="G77">
-        <v>-15.58097613851815</v>
+        <v>-16.66415353351229</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.84331630784094</v>
       </c>
       <c r="E78">
-        <v>-29.64042678044274</v>
+        <v>-31.05484582352449</v>
       </c>
       <c r="F78">
-        <v>-1.140577567427342</v>
+        <v>-1.280387760937036</v>
       </c>
       <c r="G78">
-        <v>-16.30623721307952</v>
+        <v>-16.70057946608089</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.70726416391841</v>
       </c>
       <c r="E79">
-        <v>-29.65092831166653</v>
+        <v>-31.57023145033745</v>
       </c>
       <c r="F79">
-        <v>-1.546268017846191</v>
+        <v>-1.082908285579245</v>
       </c>
       <c r="G79">
-        <v>-15.86972854154446</v>
+        <v>-16.49847893727223</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.55582770652157</v>
       </c>
       <c r="E80">
-        <v>-29.49495860989434</v>
+        <v>-31.77946732762486</v>
       </c>
       <c r="F80">
-        <v>-1.27786786729772</v>
+        <v>-1.262502480343192</v>
       </c>
       <c r="G80">
-        <v>-14.33599086447382</v>
+        <v>-16.26500933420621</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.39380852645853</v>
       </c>
       <c r="E81">
-        <v>-31.04136455640365</v>
+        <v>-31.65583093026744</v>
       </c>
       <c r="F81">
-        <v>-0.7604927817964274</v>
+        <v>-1.186487345625296</v>
       </c>
       <c r="G81">
-        <v>-14.69846249556862</v>
+        <v>-16.57959392407545</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.22981983616005</v>
       </c>
       <c r="E82">
-        <v>-31.42501008162247</v>
+        <v>-32.18635750992505</v>
       </c>
       <c r="F82">
-        <v>-1.484246493663786</v>
+        <v>-1.482867261938125</v>
       </c>
       <c r="G82">
-        <v>-15.77189695504069</v>
+        <v>-16.22822586271937</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.06377134532558</v>
       </c>
       <c r="E83">
-        <v>-32.81269980687395</v>
+        <v>-32.51846673669958</v>
       </c>
       <c r="F83">
-        <v>-1.0414393850277</v>
+        <v>-1.496706796136696</v>
       </c>
       <c r="G83">
-        <v>-16.7576764449967</v>
+        <v>-16.49521970518882</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.892836672538468</v>
       </c>
       <c r="E84">
-        <v>-31.67295761896445</v>
+        <v>-33.51112408883995</v>
       </c>
       <c r="F84">
-        <v>-1.287664140203227</v>
+        <v>-1.570975732369492</v>
       </c>
       <c r="G84">
-        <v>-15.17893521186521</v>
+        <v>-15.80772367886668</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.732953066358165</v>
       </c>
       <c r="E85">
-        <v>-32.235330692081</v>
+        <v>-33.69857347767645</v>
       </c>
       <c r="F85">
-        <v>-1.533511159843079</v>
+        <v>-1.61767660143712</v>
       </c>
       <c r="G85">
-        <v>-14.56968061881821</v>
+        <v>-16.26852844411446</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.589507376801546</v>
       </c>
       <c r="E86">
-        <v>-34.41005108596956</v>
+        <v>-34.62488415713045</v>
       </c>
       <c r="F86">
-        <v>-1.708395257554707</v>
+        <v>-1.486753133424658</v>
       </c>
       <c r="G86">
-        <v>-15.36990568657084</v>
+        <v>-16.13308906028456</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.457364481655908</v>
       </c>
       <c r="E87">
-        <v>-35.05037051794314</v>
+        <v>-35.32449037081244</v>
       </c>
       <c r="F87">
-        <v>-1.256997978951589</v>
+        <v>-1.645291885544247</v>
       </c>
       <c r="G87">
-        <v>-13.8063433047369</v>
+        <v>-16.0460233678745</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.351987571700793</v>
       </c>
       <c r="E88">
-        <v>-35.10413708983621</v>
+        <v>-36.5111996268925</v>
       </c>
       <c r="F88">
-        <v>-2.348761364819254</v>
+        <v>-1.924380460691039</v>
       </c>
       <c r="G88">
-        <v>-14.50206603672413</v>
+        <v>-15.8056512773591</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.281860538877503</v>
       </c>
       <c r="E89">
-        <v>-35.77858310193159</v>
+        <v>-37.39620156644852</v>
       </c>
       <c r="F89">
-        <v>-3.015674990608719</v>
+        <v>-1.931791863843886</v>
       </c>
       <c r="G89">
-        <v>-15.71603315433826</v>
+        <v>-15.69440701560297</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.245706667164942</v>
       </c>
       <c r="E90">
-        <v>-36.85497873118479</v>
+        <v>-37.80294004486945</v>
       </c>
       <c r="F90">
-        <v>-2.220141586553977</v>
+        <v>-1.723077241401926</v>
       </c>
       <c r="G90">
-        <v>-14.57860916013762</v>
+        <v>-16.40270319954835</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.246939428213516</v>
       </c>
       <c r="E91">
-        <v>-37.35990358304004</v>
+        <v>-39.47884902681312</v>
       </c>
       <c r="F91">
-        <v>-1.877050032397284</v>
+        <v>-1.944397958979689</v>
       </c>
       <c r="G91">
-        <v>-15.03140737099867</v>
+        <v>-15.55070782065259</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.297236476576238</v>
       </c>
       <c r="E92">
-        <v>-40.18554456655412</v>
+        <v>-39.92189680982756</v>
       </c>
       <c r="F92">
-        <v>-2.664943403896006</v>
+        <v>-2.162453252255617</v>
       </c>
       <c r="G92">
-        <v>-14.50086430869337</v>
+        <v>-15.7048335787789</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.397686219339084</v>
       </c>
       <c r="E93">
-        <v>-40.06789481183485</v>
+        <v>-41.49129155463681</v>
       </c>
       <c r="F93">
-        <v>-2.681088284576568</v>
+        <v>-2.341550426577884</v>
       </c>
       <c r="G93">
-        <v>-14.68894798768876</v>
+        <v>-15.54216992370681</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.537894198417797</v>
       </c>
       <c r="E94">
-        <v>-41.44956845936714</v>
+        <v>-42.61707245718066</v>
       </c>
       <c r="F94">
-        <v>-3.081869001399025</v>
+        <v>-2.529816799681739</v>
       </c>
       <c r="G94">
-        <v>-14.06814786707355</v>
+        <v>-15.68111683053556</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.729631097560212</v>
       </c>
       <c r="E95">
-        <v>-42.11391597442541</v>
+        <v>-44.14509279921883</v>
       </c>
       <c r="F95">
-        <v>-2.828086222040354</v>
+        <v>-2.548366430932628</v>
       </c>
       <c r="G95">
-        <v>-14.49720450059971</v>
+        <v>-15.80019880885592</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.974481208298513</v>
       </c>
       <c r="E96">
-        <v>-42.63938877709046</v>
+        <v>-45.61248593124231</v>
       </c>
       <c r="F96">
-        <v>-4.001158838697207</v>
+        <v>-2.858426834902692</v>
       </c>
       <c r="G96">
-        <v>-13.40092727690667</v>
+        <v>-15.97803634940726</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.25428356468568</v>
       </c>
       <c r="E97">
-        <v>-45.07824373866141</v>
+        <v>-46.48018004314102</v>
       </c>
       <c r="F97">
-        <v>-3.959517637725879</v>
+        <v>-2.866971444662568</v>
       </c>
       <c r="G97">
-        <v>-13.08581631029669</v>
+        <v>-16.18723137730657</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.5784868767314</v>
       </c>
       <c r="E98">
-        <v>-47.32531556177051</v>
+        <v>-48.92215965177726</v>
       </c>
       <c r="F98">
-        <v>-4.258868079545147</v>
+        <v>-2.911494535828237</v>
       </c>
       <c r="G98">
-        <v>-14.13988738890955</v>
+        <v>-16.13524919124894</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.93054471656015</v>
       </c>
       <c r="E99">
-        <v>-49.57993635105041</v>
+        <v>-50.12947799306622</v>
       </c>
       <c r="F99">
-        <v>-3.767087890055553</v>
+        <v>-3.054210642186952</v>
       </c>
       <c r="G99">
-        <v>-14.02671970019511</v>
+        <v>-16.1590520136763</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.31854117032276</v>
       </c>
       <c r="E100">
-        <v>-50.45347445865601</v>
+        <v>-51.77338311707918</v>
       </c>
       <c r="F100">
-        <v>-5.083305707385772</v>
+        <v>-3.151474229154059</v>
       </c>
       <c r="G100">
-        <v>-14.10076667227199</v>
+        <v>-16.41352371764345</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.6917935469078</v>
       </c>
       <c r="E101">
-        <v>-52.29312966436153</v>
+        <v>-53.33170574293968</v>
       </c>
       <c r="F101">
-        <v>-4.479556752794575</v>
+        <v>-3.516090081905095</v>
       </c>
       <c r="G101">
-        <v>-14.95742826510534</v>
+        <v>-16.09054192901385</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.10616841263411</v>
       </c>
       <c r="E102">
-        <v>-52.58359730839852</v>
+        <v>-54.82524288752793</v>
       </c>
       <c r="F102">
-        <v>-5.295807625593332</v>
+        <v>-3.579254753103363</v>
       </c>
       <c r="G102">
-        <v>-15.81116664622752</v>
+        <v>-16.51268614345402</v>
       </c>
     </row>
   </sheetData>
